--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -105,7 +105,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T07:06:08.449Z</t>
+          <t xml:space="preserve">2026-10-14T07:43:15.547Z</t>
         </is>
       </c>
     </row>
@@ -407,7 +407,8 @@
     <col min="3" max="3" width="21.2" customWidth="1"/>
     <col min="4" max="4" width="13.2" customWidth="1"/>
     <col min="5" max="5" width="22.8" customWidth="1"/>
-    <col min="6" max="6" width="19.6" customWidth="1"/>
+    <col min="6" max="6" width="30.8" customWidth="1"/>
+    <col min="7" max="7" width="19.6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,6 +439,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>progress_area_mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>disease_max</t>
         </is>
       </c>
@@ -461,6 +467,9 @@
         <v>0.039306</v>
       </c>
       <c r="F2">
+        <v>0.03829</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
     </row>
@@ -483,6 +492,9 @@
         <v>0.090419</v>
       </c>
       <c r="F3">
+        <v>0.088226</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
     </row>
@@ -505,6 +517,9 @@
         <v>0.145113</v>
       </c>
       <c r="F4">
+        <v>0.141565</v>
+      </c>
+      <c r="G4">
         <v>4</v>
       </c>
     </row>
@@ -527,6 +542,9 @@
         <v>0.194113</v>
       </c>
       <c r="F5">
+        <v>0.189452</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>
@@ -549,6 +567,9 @@
         <v>0.247806</v>
       </c>
       <c r="F6">
+        <v>0.241968</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
@@ -571,6 +592,9 @@
         <v>0.298548</v>
       </c>
       <c r="F7">
+        <v>0.291435</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>
@@ -593,6 +617,9 @@
         <v>0.3385</v>
       </c>
       <c r="F8">
+        <v>0.331226</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>
@@ -615,6 +642,9 @@
         <v>0.345242</v>
       </c>
       <c r="F9">
+        <v>0.338129</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>
@@ -637,6 +667,9 @@
         <v>0.346371</v>
       </c>
       <c r="F10">
+        <v>0.339129</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>
@@ -659,6 +692,9 @@
         <v>0.352032</v>
       </c>
       <c r="F11">
+        <v>0.345032</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>
@@ -681,6 +717,9 @@
         <v>0.363452</v>
       </c>
       <c r="F12">
+        <v>0.357548</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>
@@ -703,6 +742,9 @@
         <v>0.378468</v>
       </c>
       <c r="F13">
+        <v>0.373435</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>
@@ -725,6 +767,9 @@
         <v>0.38721</v>
       </c>
       <c r="F14">
+        <v>0.38229</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>
@@ -747,6 +792,9 @@
         <v>0.392258</v>
       </c>
       <c r="F15">
+        <v>0.387468</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>
@@ -769,6 +817,9 @@
         <v>0.397161</v>
       </c>
       <c r="F16">
+        <v>0.392468</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>
@@ -791,6 +842,9 @@
         <v>0.399565</v>
       </c>
       <c r="F17">
+        <v>0.394871</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>
@@ -813,6 +867,9 @@
         <v>0.403048</v>
       </c>
       <c r="F18">
+        <v>0.398468</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>
@@ -835,6 +892,9 @@
         <v>0.403774</v>
       </c>
       <c r="F19">
+        <v>0.399258</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>
@@ -857,6 +917,9 @@
         <v>0.405839</v>
       </c>
       <c r="F20">
+        <v>0.401435</v>
+      </c>
+      <c r="G20">
         <v>5</v>
       </c>
     </row>
@@ -879,6 +942,9 @@
         <v>0.405839</v>
       </c>
       <c r="F21">
+        <v>0.401435</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
     </row>
@@ -901,6 +967,9 @@
         <v>0.409</v>
       </c>
       <c r="F22">
+        <v>0.404548</v>
+      </c>
+      <c r="G22">
         <v>5</v>
       </c>
     </row>
@@ -923,6 +992,9 @@
         <v>0.409387</v>
       </c>
       <c r="F23">
+        <v>0.405</v>
+      </c>
+      <c r="G23">
         <v>5</v>
       </c>
     </row>
@@ -945,6 +1017,9 @@
         <v>0.410323</v>
       </c>
       <c r="F24">
+        <v>0.406</v>
+      </c>
+      <c r="G24">
         <v>5</v>
       </c>
     </row>
@@ -967,6 +1042,9 @@
         <v>0.416581</v>
       </c>
       <c r="F25">
+        <v>0.412323</v>
+      </c>
+      <c r="G25">
         <v>5</v>
       </c>
     </row>
@@ -989,6 +1067,9 @@
         <v>0.425726</v>
       </c>
       <c r="F26">
+        <v>0.421758</v>
+      </c>
+      <c r="G26">
         <v>5</v>
       </c>
     </row>
@@ -1011,6 +1092,9 @@
         <v>0.432097</v>
       </c>
       <c r="F27">
+        <v>0.428258</v>
+      </c>
+      <c r="G27">
         <v>5</v>
       </c>
     </row>
@@ -1033,6 +1117,9 @@
         <v>0.446806</v>
       </c>
       <c r="F28">
+        <v>0.443274</v>
+      </c>
+      <c r="G28">
         <v>5</v>
       </c>
     </row>
@@ -1055,6 +1142,9 @@
         <v>0.423645</v>
       </c>
       <c r="F29">
+        <v>0.432597</v>
+      </c>
+      <c r="G29">
         <v>5</v>
       </c>
     </row>
@@ -1077,6 +1167,9 @@
         <v>0.384016</v>
       </c>
       <c r="F30">
+        <v>0.394242</v>
+      </c>
+      <c r="G30">
         <v>5</v>
       </c>
     </row>
@@ -1099,6 +1192,9 @@
         <v>0.363516</v>
       </c>
       <c r="F31">
+        <v>0.374935</v>
+      </c>
+      <c r="G31">
         <v>5</v>
       </c>
     </row>
@@ -1121,6 +1217,9 @@
         <v>0.254613</v>
       </c>
       <c r="F32">
+        <v>0.253613</v>
+      </c>
+      <c r="G32">
         <v>5</v>
       </c>
     </row>
@@ -1143,6 +1242,9 @@
         <v>0.235887</v>
       </c>
       <c r="F33">
+        <v>0.237629</v>
+      </c>
+      <c r="G33">
         <v>5</v>
       </c>
     </row>
@@ -1165,6 +1267,9 @@
         <v>0.287</v>
       </c>
       <c r="F34">
+        <v>0.288371</v>
+      </c>
+      <c r="G34">
         <v>5</v>
       </c>
     </row>
@@ -1187,6 +1292,9 @@
         <v>0.351935</v>
       </c>
       <c r="F35">
+        <v>0.352952</v>
+      </c>
+      <c r="G35">
         <v>5</v>
       </c>
     </row>
@@ -1209,6 +1317,9 @@
         <v>0.427258</v>
       </c>
       <c r="F36">
+        <v>0.428</v>
+      </c>
+      <c r="G36">
         <v>5</v>
       </c>
     </row>
@@ -1231,6 +1342,9 @@
         <v>0.515629</v>
       </c>
       <c r="F37">
+        <v>0.516097</v>
+      </c>
+      <c r="G37">
         <v>5</v>
       </c>
     </row>
@@ -1253,6 +1367,9 @@
         <v>0.587161</v>
       </c>
       <c r="F38">
+        <v>0.587677</v>
+      </c>
+      <c r="G38">
         <v>5</v>
       </c>
     </row>
@@ -1275,6 +1392,9 @@
         <v>0.653565</v>
       </c>
       <c r="F39">
+        <v>0.653581</v>
+      </c>
+      <c r="G39">
         <v>5</v>
       </c>
     </row>
@@ -1297,6 +1417,9 @@
         <v>0.701032</v>
       </c>
       <c r="F40">
+        <v>0.699935</v>
+      </c>
+      <c r="G40">
         <v>5</v>
       </c>
     </row>
@@ -1319,6 +1442,9 @@
         <v>0.736113</v>
       </c>
       <c r="F41">
+        <v>0.734742</v>
+      </c>
+      <c r="G41">
         <v>5</v>
       </c>
     </row>
@@ -1341,6 +1467,9 @@
         <v>0.772016</v>
       </c>
       <c r="F42">
+        <v>0.771758</v>
+      </c>
+      <c r="G42">
         <v>5</v>
       </c>
     </row>
@@ -1363,6 +1492,9 @@
         <v>0.796194</v>
       </c>
       <c r="F43">
+        <v>0.796694</v>
+      </c>
+      <c r="G43">
         <v>5</v>
       </c>
     </row>
@@ -1385,6 +1517,9 @@
         <v>0.813952</v>
       </c>
       <c r="F44">
+        <v>0.814887</v>
+      </c>
+      <c r="G44">
         <v>5</v>
       </c>
     </row>
@@ -1407,6 +1542,9 @@
         <v>0.818065</v>
       </c>
       <c r="F45">
+        <v>0.820484</v>
+      </c>
+      <c r="G45">
         <v>5</v>
       </c>
     </row>
@@ -1429,6 +1567,9 @@
         <v>0.802387</v>
       </c>
       <c r="F46">
+        <v>0.800935</v>
+      </c>
+      <c r="G46">
         <v>5</v>
       </c>
     </row>
@@ -1451,6 +1592,9 @@
         <v>0.68379</v>
       </c>
       <c r="F47">
+        <v>0.686516</v>
+      </c>
+      <c r="G47">
         <v>5</v>
       </c>
     </row>
@@ -1473,6 +1617,9 @@
         <v>0.579823</v>
       </c>
       <c r="F48">
+        <v>0.5675</v>
+      </c>
+      <c r="G48">
         <v>5</v>
       </c>
     </row>
@@ -1495,6 +1642,9 @@
         <v>0.509129</v>
       </c>
       <c r="F49">
+        <v>0.502597</v>
+      </c>
+      <c r="G49">
         <v>5</v>
       </c>
     </row>
@@ -1517,6 +1667,9 @@
         <v>0.470726</v>
       </c>
       <c r="F50">
+        <v>0.462935</v>
+      </c>
+      <c r="G50">
         <v>5</v>
       </c>
     </row>
@@ -1539,6 +1692,9 @@
         <v>0.479581</v>
       </c>
       <c r="F51">
+        <v>0.471871</v>
+      </c>
+      <c r="G51">
         <v>5</v>
       </c>
     </row>
@@ -1561,6 +1717,9 @@
         <v>0.479952</v>
       </c>
       <c r="F52">
+        <v>0.47229</v>
+      </c>
+      <c r="G52">
         <v>5</v>
       </c>
     </row>
@@ -1583,6 +1742,9 @@
         <v>0.484258</v>
       </c>
       <c r="F53">
+        <v>0.476645</v>
+      </c>
+      <c r="G53">
         <v>5</v>
       </c>
     </row>
@@ -1605,6 +1767,9 @@
         <v>0.488194</v>
       </c>
       <c r="F54">
+        <v>0.480645</v>
+      </c>
+      <c r="G54">
         <v>5</v>
       </c>
     </row>
@@ -1627,11 +1792,14 @@
         <v>0.488258</v>
       </c>
       <c r="F55">
+        <v>0.480774</v>
+      </c>
+      <c r="G55">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:G55"/>
 </worksheet>
 </file>
 

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -10,10 +10,11 @@
     <sheet name="q5 联合筛选：运距远 + 有机碳低 + 病级高的地块" sheetId="6" r:id="rId6"/>
     <sheet name="q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）" sheetId="7" r:id="rId7"/>
     <sheet name="q7 管理分区 × 作物 的地块数与面积" sheetId="8" r:id="rId8"/>
-    <sheet name="q8 区域逐日 → 按年月汇总" sheetId="9" r:id="rId9"/>
-    <sheet name="q9 农事事件 → 按年 × 类型计数" sheetId="10" r:id="rId10"/>
-    <sheet name="q10 地块季 → 按作物汇总" sheetId="11" r:id="rId11"/>
-    <sheet name="q11 单元 × 旬 → 按旬汇总" sheetId="12" r:id="rId12"/>
+    <sheet name="q12 单产两套口径对照（季等权 vs 面积加权）" sheetId="9" r:id="rId9"/>
+    <sheet name="q8 区域逐日 → 按年月汇总" sheetId="10" r:id="rId10"/>
+    <sheet name="q9 农事事件 → 按年 × 类型计数" sheetId="11" r:id="rId11"/>
+    <sheet name="q10 地块季 → 按作物汇总" sheetId="12" r:id="rId12"/>
+    <sheet name="q11 单元 × 旬 → 按旬汇总" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -105,7 +106,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T07:43:15.547Z</t>
+          <t xml:space="preserve">2026-10-14T09:01:11.228Z</t>
         </is>
       </c>
     </row>
@@ -165,7 +166,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总</t>
+          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总</t>
         </is>
       </c>
     </row>
@@ -175,6 +176,451 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="18.0" customWidth="1"/>
+    <col min="2" max="2" width="11.6" customWidth="1"/>
+    <col min="3" max="3" width="22.8" customWidth="1"/>
+    <col min="4" max="4" width="29.2" customWidth="1"/>
+    <col min="5" max="5" width="22.8" customWidth="1"/>
+    <col min="6" max="6" width="19.6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year_month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n_days</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precip_sum_mm</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>humidity_mean_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>progress_mean</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>disease_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202407</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>31</v>
+      </c>
+      <c r="C2">
+        <v>106.51</v>
+      </c>
+      <c r="D2">
+        <v>78.774194</v>
+      </c>
+      <c r="E2">
+        <v>0.074548</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202408</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>114.970002</v>
+      </c>
+      <c r="D3">
+        <v>79.096774</v>
+      </c>
+      <c r="E3">
+        <v>0.239645</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202409</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>171.119999</v>
+      </c>
+      <c r="D4">
+        <v>83.5</v>
+      </c>
+      <c r="E4">
+        <v>0.360767</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202410</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>31</v>
+      </c>
+      <c r="C5">
+        <v>57.44</v>
+      </c>
+      <c r="D5">
+        <v>91</v>
+      </c>
+      <c r="E5">
+        <v>0.39129</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202411</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>40.33</v>
+      </c>
+      <c r="D6">
+        <v>91.633333</v>
+      </c>
+      <c r="E6">
+        <v>0.4338</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202412</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>48.49</v>
+      </c>
+      <c r="D7">
+        <v>92.16129</v>
+      </c>
+      <c r="E7">
+        <v>0.449677</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202501</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <v>70.31</v>
+      </c>
+      <c r="D8">
+        <v>92.548387</v>
+      </c>
+      <c r="E8">
+        <v>0.456194</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202502</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>19.29</v>
+      </c>
+      <c r="D9">
+        <v>90.321429</v>
+      </c>
+      <c r="E9">
+        <v>0.46275</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202503</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>31</v>
+      </c>
+      <c r="C10">
+        <v>45.03</v>
+      </c>
+      <c r="D10">
+        <v>81.129032</v>
+      </c>
+      <c r="E10">
+        <v>0.488839</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202504</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>24.55</v>
+      </c>
+      <c r="D11">
+        <v>76.866667</v>
+      </c>
+      <c r="E11">
+        <v>0.487033</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202505</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>59.33</v>
+      </c>
+      <c r="D12">
+        <v>73.064516</v>
+      </c>
+      <c r="E12">
+        <v>0.329452</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202506</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>30</v>
+      </c>
+      <c r="C13">
+        <v>95.51</v>
+      </c>
+      <c r="D13">
+        <v>75.433333</v>
+      </c>
+      <c r="E13">
+        <v>0.492333</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202507</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>31</v>
+      </c>
+      <c r="C14">
+        <v>128.100002</v>
+      </c>
+      <c r="D14">
+        <v>77.225806</v>
+      </c>
+      <c r="E14">
+        <v>0.755161</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202508</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>93.52</v>
+      </c>
+      <c r="D15">
+        <v>74.870968</v>
+      </c>
+      <c r="E15">
+        <v>0.901258</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202509</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>97.05</v>
+      </c>
+      <c r="D16">
+        <v>83.066667</v>
+      </c>
+      <c r="E16">
+        <v>0.967867</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202510</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>31</v>
+      </c>
+      <c r="C17">
+        <v>50.000001</v>
+      </c>
+      <c r="D17">
+        <v>85.548387</v>
+      </c>
+      <c r="E17">
+        <v>0.72471</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202511</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>60.129999</v>
+      </c>
+      <c r="D18">
+        <v>90.633333</v>
+      </c>
+      <c r="E18">
+        <v>0.523467</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202512</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>31</v>
+      </c>
+      <c r="C19">
+        <v>20.64</v>
+      </c>
+      <c r="D19">
+        <v>94.032258</v>
+      </c>
+      <c r="E19">
+        <v>0.534161</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -279,7 +725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -398,7 +844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -37202,443 +37648,205 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.0" customWidth="1"/>
-    <col min="2" max="2" width="11.6" customWidth="1"/>
-    <col min="3" max="3" width="22.8" customWidth="1"/>
-    <col min="4" max="4" width="29.2" customWidth="1"/>
+    <col min="1" max="1" width="23.5" customWidth="1"/>
+    <col min="2" max="2" width="16.4" customWidth="1"/>
+    <col min="3" max="3" width="13.2" customWidth="1"/>
+    <col min="4" max="4" width="22.8" customWidth="1"/>
     <col min="5" max="5" width="22.8" customWidth="1"/>
-    <col min="6" max="6" width="19.6" customWidth="1"/>
+    <col min="6" max="6" width="26.0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>year_month</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n_days</t>
+          <t>n_seasons</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>precip_sum_mm</t>
+          <t>area_ha</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>humidity_mean_pct</t>
+          <t>yield_t_total</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>progress_mean</t>
+          <t>yield_t_ha_eq</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>disease_max</t>
+          <t>yield_t_ha_area</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202407</t>
+          <t xml:space="preserve">冬大麦 · 籽粒 · 2025</t>
         </is>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C2">
-        <v>106.51</v>
+        <v>104.045</v>
       </c>
       <c r="D2">
-        <v>78.774194</v>
+        <v>655.4</v>
       </c>
       <c r="E2">
-        <v>0.074548</v>
+        <v>6.200851</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>6.299197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202408</t>
+          <t xml:space="preserve">冬大麦 · 籽粒 · 2026</t>
         </is>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C3">
-        <v>114.970002</v>
-      </c>
-      <c r="D3">
-        <v>79.096774</v>
-      </c>
-      <c r="E3">
-        <v>0.239645</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>104.045</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">202409</t>
+          <t xml:space="preserve">冬小麦 · 籽粒 · 2025</t>
         </is>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="C4">
-        <v>171.119999</v>
+        <v>249.652</v>
       </c>
       <c r="D4">
-        <v>83.5</v>
+        <v>1595.9</v>
       </c>
       <c r="E4">
-        <v>0.360767</v>
+        <v>6.367909</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6.392498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">202410</t>
+          <t xml:space="preserve">冬小麦 · 籽粒 · 2026</t>
         </is>
       </c>
       <c r="B5">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C5">
-        <v>57.44</v>
-      </c>
-      <c r="D5">
-        <v>91</v>
-      </c>
-      <c r="E5">
-        <v>0.39129</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
+        <v>249.652</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">202411</t>
+          <t xml:space="preserve">啤酒花 · 干花 · 2024</t>
         </is>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>40.33</v>
+        <v>60.62</v>
       </c>
       <c r="D6">
-        <v>91.633333</v>
+        <v>115.6</v>
       </c>
       <c r="E6">
-        <v>0.4338</v>
+        <v>1.905938</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>1.906961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">202412</t>
+          <t xml:space="preserve">啤酒花 · 干花 · 2025</t>
         </is>
       </c>
       <c r="B7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>48.49</v>
+        <v>60.62</v>
       </c>
       <c r="D7">
-        <v>92.16129</v>
+        <v>119.5</v>
       </c>
       <c r="E7">
-        <v>0.449677</v>
+        <v>1.932812</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1.971297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">202501</t>
+          <t xml:space="preserve">青贮玉米 · 鲜重 · 2024</t>
         </is>
       </c>
       <c r="B8">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="C8">
-        <v>70.31</v>
+        <v>248.767</v>
       </c>
       <c r="D8">
-        <v>92.548387</v>
+        <v>9201.5</v>
       </c>
       <c r="E8">
-        <v>0.456194</v>
+        <v>37.213462</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>36.988427</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">202502</t>
+          <t xml:space="preserve">青贮玉米 · 鲜重 · 2025</t>
         </is>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="C9">
-        <v>19.29</v>
+        <v>248.767</v>
       </c>
       <c r="D9">
-        <v>90.321429</v>
+        <v>9306.9</v>
       </c>
       <c r="E9">
-        <v>0.46275</v>
+        <v>38.065385</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202503</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>31</v>
-      </c>
-      <c r="C10">
-        <v>45.03</v>
-      </c>
-      <c r="D10">
-        <v>81.129032</v>
-      </c>
-      <c r="E10">
-        <v>0.488839</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202504</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>30</v>
-      </c>
-      <c r="C11">
-        <v>24.55</v>
-      </c>
-      <c r="D11">
-        <v>76.866667</v>
-      </c>
-      <c r="E11">
-        <v>0.487033</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202505</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>31</v>
-      </c>
-      <c r="C12">
-        <v>59.33</v>
-      </c>
-      <c r="D12">
-        <v>73.064516</v>
-      </c>
-      <c r="E12">
-        <v>0.329452</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202506</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>30</v>
-      </c>
-      <c r="C13">
-        <v>95.51</v>
-      </c>
-      <c r="D13">
-        <v>75.433333</v>
-      </c>
-      <c r="E13">
-        <v>0.492333</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202507</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>31</v>
-      </c>
-      <c r="C14">
-        <v>128.100002</v>
-      </c>
-      <c r="D14">
-        <v>77.225806</v>
-      </c>
-      <c r="E14">
-        <v>0.755161</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202508</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>31</v>
-      </c>
-      <c r="C15">
-        <v>93.52</v>
-      </c>
-      <c r="D15">
-        <v>74.870968</v>
-      </c>
-      <c r="E15">
-        <v>0.901258</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202509</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>30</v>
-      </c>
-      <c r="C16">
-        <v>97.05</v>
-      </c>
-      <c r="D16">
-        <v>83.066667</v>
-      </c>
-      <c r="E16">
-        <v>0.967867</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202510</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>31</v>
-      </c>
-      <c r="C17">
-        <v>50.000001</v>
-      </c>
-      <c r="D17">
-        <v>85.548387</v>
-      </c>
-      <c r="E17">
-        <v>0.72471</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202511</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>30</v>
-      </c>
-      <c r="C18">
-        <v>60.129999</v>
-      </c>
-      <c r="D18">
-        <v>90.633333</v>
-      </c>
-      <c r="E18">
-        <v>0.523467</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202512</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>31</v>
-      </c>
-      <c r="C19">
-        <v>20.64</v>
-      </c>
-      <c r="D19">
-        <v>94.032258</v>
-      </c>
-      <c r="E19">
-        <v>0.534161</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
+        <v>37.412117</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F19"/>
+  <autoFilter ref="A1:F9"/>
 </worksheet>
 </file>
--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -106,7 +106,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T09:01:11.228Z</t>
+          <t xml:space="preserve">2026-10-14T10:56:56.118Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -106,7 +106,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T10:56:56.118Z</t>
+          <t xml:space="preserve">2026-10-14T14:05:13.624Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -106,7 +106,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T14:05:13.624Z</t>
+          <t xml:space="preserve">2026-10-14T18:29:13.148Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -15,6 +15,7 @@
     <sheet name="q9 农事事件 → 按年 × 类型计数" sheetId="11" r:id="rId11"/>
     <sheet name="q10 地块季 → 按作物汇总" sheetId="12" r:id="rId12"/>
     <sheet name="q11 单元 × 旬 → 按旬汇总" sheetId="13" r:id="rId13"/>
+    <sheet name="q13 农事日历：月 × 事件类型（次）" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -106,7 +107,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T18:29:13.148Z</t>
+          <t xml:space="preserve">2026-10-14T18:59:39.717Z</t>
         </is>
       </c>
     </row>
@@ -166,7 +167,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总</t>
+          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总; q13 农事日历：月 × 事件类型（次）</t>
         </is>
       </c>
     </row>
@@ -2246,6 +2247,270 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G55"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="8.6" customWidth="1"/>
+    <col min="2" max="2" width="6.8" customWidth="1"/>
+    <col min="3" max="3" width="16.4" customWidth="1"/>
+    <col min="4" max="4" width="13.2" customWidth="1"/>
+    <col min="5" max="5" width="5.8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ym</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sow</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>fertilize</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>harvest</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-10</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>116</v>
+      </c>
+      <c r="C2">
+        <v>111</v>
+      </c>
+      <c r="E2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>157</v>
+      </c>
+      <c r="E3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>128</v>
+      </c>
+      <c r="C4">
+        <v>108</v>
+      </c>
+      <c r="E4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-07</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>322</v>
+      </c>
+      <c r="D5">
+        <v>178</v>
+      </c>
+      <c r="E5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-06</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>178</v>
+      </c>
+      <c r="E6">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-11</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-04</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>57</v>
+      </c>
+      <c r="E8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-09</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>144</v>
+      </c>
+      <c r="E9">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>104</v>
+      </c>
+      <c r="E10">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-09</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>144</v>
+      </c>
+      <c r="E11">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>38</v>
+      </c>
+      <c r="E12">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>59</v>
+      </c>
+      <c r="C13">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-05</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>79</v>
+      </c>
+      <c r="E14">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合计</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>586</v>
+      </c>
+      <c r="C15">
+        <v>772</v>
+      </c>
+      <c r="D15">
+        <v>801</v>
+      </c>
+      <c r="E15">
+        <v>2159</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E15"/>
 </worksheet>
 </file>
 

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -107,7 +107,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T18:59:39.717Z</t>
+          <t xml:space="preserve">2026-10-14T19:29:49.474Z</t>
         </is>
       </c>
     </row>
@@ -2291,75 +2291,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-10</t>
+          <t xml:space="preserve">2024-04</t>
         </is>
       </c>
       <c r="B2">
-        <v>116</v>
-      </c>
-      <c r="C2">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="E2">
-        <v>227</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>157</v>
+          <t xml:space="preserve">2024-05</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>79</v>
       </c>
       <c r="E3">
-        <v>157</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>128</v>
+          <t xml:space="preserve">2024-07</t>
+        </is>
       </c>
       <c r="C4">
-        <v>108</v>
+        <v>322</v>
+      </c>
+      <c r="D4">
+        <v>178</v>
       </c>
       <c r="E4">
-        <v>236</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07</t>
-        </is>
+          <t xml:space="preserve">2024-09</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>322</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>178</v>
+          <t xml:space="preserve">2024-10</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>116</v>
+      </c>
+      <c r="C6">
+        <v>111</v>
       </c>
       <c r="E6">
-        <v>178</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
@@ -2381,113 +2384,110 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04</t>
+          <t xml:space="preserve">2025-04</t>
         </is>
       </c>
       <c r="B8">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>57</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09</t>
+          <t xml:space="preserve">2025-05</t>
         </is>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="E9">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>104</v>
+          <t xml:space="preserve">2025-06</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>178</v>
       </c>
       <c r="E10">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>11</v>
+          <t xml:space="preserve">2025-07</t>
+        </is>
       </c>
       <c r="D11">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E11">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11</t>
+          <t xml:space="preserve">2025-09</t>
         </is>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>38</v>
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>144</v>
       </c>
       <c r="E12">
-        <v>54</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04</t>
+          <t xml:space="preserve">2025-10</t>
         </is>
       </c>
       <c r="B13">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="C13">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="E13">
-        <v>91</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05</t>
+          <t xml:space="preserve">2025-11</t>
         </is>
       </c>
       <c r="B14">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>38</v>
       </c>
       <c r="E14">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2558,7 +2558,7 @@
           <t xml:space="preserve">冬小麦 · 籽粒</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>6.368</v>
       </c>
       <c r="E2">
@@ -2571,7 +2571,7 @@
           <t xml:space="preserve">冬大麦 · 籽粒</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>6.201</v>
       </c>
       <c r="E3">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B4">
+        <v>37.213</v>
+      </c>
+      <c r="C4">
         <v>38.065</v>
-      </c>
-      <c r="D4">
-        <v>37.213</v>
       </c>
       <c r="E4">
         <v>37.639</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B5">
+        <v>1.906</v>
+      </c>
+      <c r="C5">
         <v>1.933</v>
-      </c>
-      <c r="D5">
-        <v>1.906</v>
       </c>
       <c r="E5">
         <v>1.919</v>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.906</v>
+      </c>
+      <c r="C6">
         <v>17.108</v>
-      </c>
-      <c r="D6">
-        <v>28.906</v>
       </c>
       <c r="E6">
         <v>20.848</v>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -15,7 +15,8 @@
     <sheet name="q9 农事事件 → 按年 × 类型计数" sheetId="11" r:id="rId11"/>
     <sheet name="q10 地块季 → 按作物汇总" sheetId="12" r:id="rId12"/>
     <sheet name="q11 单元 × 旬 → 按旬汇总" sheetId="13" r:id="rId13"/>
-    <sheet name="q13 农事日历：月 × 事件类型（次）" sheetId="14" r:id="rId14"/>
+    <sheet name="q14 收获排产压力（按日）" sheetId="14" r:id="rId14"/>
+    <sheet name="q13 农事日历：月 × 事件类型（次）" sheetId="15" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>
@@ -107,7 +108,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T19:29:49.474Z</t>
+          <t xml:space="preserve">2026-10-14T19:53:32.768Z</t>
         </is>
       </c>
     </row>
@@ -167,7 +168,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总; q13 农事日历：月 × 事件类型（次）</t>
+          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总; q14 收获排产压力（按日）; q13 农事日历：月 × 事件类型（次）</t>
         </is>
       </c>
     </row>
@@ -684,16 +685,16 @@
         <v>479</v>
       </c>
       <c r="D2">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="E2">
-        <v>1094</v>
+        <v>916</v>
       </c>
       <c r="F2">
-        <v>5828.49</v>
+        <v>4009.22</v>
       </c>
       <c r="G2">
-        <v>322</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
@@ -715,7 +716,7 @@
         <v>1065</v>
       </c>
       <c r="F3">
-        <v>6790.68</v>
+        <v>6780.56</v>
       </c>
       <c r="G3">
         <v>479</v>
@@ -774,10 +775,10 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>235.1</v>
+        <v>224</v>
       </c>
       <c r="D2">
-        <v>1.919375</v>
+        <v>1.891563</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -793,10 +794,10 @@
         <v>208</v>
       </c>
       <c r="C3">
-        <v>18508.4</v>
+        <v>18392.9</v>
       </c>
       <c r="D3">
-        <v>37.639423</v>
+        <v>37.540192</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -812,10 +813,10 @@
         <v>94</v>
       </c>
       <c r="C4">
-        <v>655.4</v>
+        <v>650.8</v>
       </c>
       <c r="D4">
-        <v>6.200851</v>
+        <v>6.292979</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -831,10 +832,10 @@
         <v>220</v>
       </c>
       <c r="C5">
-        <v>1595.9</v>
+        <v>1624.4</v>
       </c>
       <c r="D5">
-        <v>6.367909</v>
+        <v>6.434545</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -905,7 +906,7 @@
         <v>62</v>
       </c>
       <c r="C2">
-        <v>292.6</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -2251,6 +2252,539 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="9.6" customWidth="1"/>
+    <col min="2" max="2" width="16.4" customWidth="1"/>
+    <col min="3" max="3" width="13.2" customWidth="1"/>
+    <col min="4" max="4" width="13.2" customWidth="1"/>
+    <col min="5" max="5" width="13.2" customWidth="1"/>
+    <col min="6" max="6" width="18.0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n_parcels</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>area_ha</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>yield_t</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>t_min_w</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>haul_t_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20240905</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>60.62</v>
+      </c>
+      <c r="D2">
+        <v>112.2</v>
+      </c>
+      <c r="E2">
+        <v>5.008146</v>
+      </c>
+      <c r="F2">
+        <v>561.914</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20240920</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>104</v>
+      </c>
+      <c r="C3">
+        <v>248.767</v>
+      </c>
+      <c r="D3">
+        <v>9117.1</v>
+      </c>
+      <c r="E3">
+        <v>4.913318</v>
+      </c>
+      <c r="F3">
+        <v>44795.208</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250701</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>32.619</v>
+      </c>
+      <c r="D4">
+        <v>194.5</v>
+      </c>
+      <c r="E4">
+        <v>4.352889</v>
+      </c>
+      <c r="F4">
+        <v>846.637</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250702</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>12.069</v>
+      </c>
+      <c r="D5">
+        <v>79.8</v>
+      </c>
+      <c r="E5">
+        <v>11.111366</v>
+      </c>
+      <c r="F5">
+        <v>886.687</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250703</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0.806</v>
+      </c>
+      <c r="D6">
+        <v>4.3</v>
+      </c>
+      <c r="E6">
+        <v>4.9</v>
+      </c>
+      <c r="F6">
+        <v>21.07</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250704</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>8.5</v>
+      </c>
+      <c r="D7">
+        <v>60.6</v>
+      </c>
+      <c r="E7">
+        <v>6.812343</v>
+      </c>
+      <c r="F7">
+        <v>412.828</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250705</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>50.051</v>
+      </c>
+      <c r="D8">
+        <v>311.6</v>
+      </c>
+      <c r="E8">
+        <v>4.728963</v>
+      </c>
+      <c r="F8">
+        <v>1473.545</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250721</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>9.078</v>
+      </c>
+      <c r="D9">
+        <v>57.9</v>
+      </c>
+      <c r="E9">
+        <v>5.576632</v>
+      </c>
+      <c r="F9">
+        <v>322.887</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250722</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>21.916</v>
+      </c>
+      <c r="D10">
+        <v>139.2</v>
+      </c>
+      <c r="E10">
+        <v>4.894497</v>
+      </c>
+      <c r="F10">
+        <v>681.314</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250723</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>21.821</v>
+      </c>
+      <c r="D11">
+        <v>140.1</v>
+      </c>
+      <c r="E11">
+        <v>5.96955</v>
+      </c>
+      <c r="F11">
+        <v>836.334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250724</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>17.585</v>
+      </c>
+      <c r="D12">
+        <v>112</v>
+      </c>
+      <c r="E12">
+        <v>5.666027</v>
+      </c>
+      <c r="F12">
+        <v>634.595</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250725</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>83</v>
+      </c>
+      <c r="C13">
+        <v>179.252</v>
+      </c>
+      <c r="D13">
+        <v>1175.2</v>
+      </c>
+      <c r="E13">
+        <v>5.744972</v>
+      </c>
+      <c r="F13">
+        <v>6751.491</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250901</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>60.62</v>
+      </c>
+      <c r="D14">
+        <v>111.8</v>
+      </c>
+      <c r="E14">
+        <v>4.953784</v>
+      </c>
+      <c r="F14">
+        <v>553.833</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250908</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>45.6</v>
+      </c>
+      <c r="D15">
+        <v>1847.5</v>
+      </c>
+      <c r="E15">
+        <v>5.236645</v>
+      </c>
+      <c r="F15">
+        <v>9674.702</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250909</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>18.641</v>
+      </c>
+      <c r="D16">
+        <v>666.9</v>
+      </c>
+      <c r="E16">
+        <v>4.851209</v>
+      </c>
+      <c r="F16">
+        <v>3235.271</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250911</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>2.768</v>
+      </c>
+      <c r="D17">
+        <v>100.7</v>
+      </c>
+      <c r="E17">
+        <v>3.560665</v>
+      </c>
+      <c r="F17">
+        <v>358.559</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250912</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>24.792</v>
+      </c>
+      <c r="D18">
+        <v>759.4</v>
+      </c>
+      <c r="E18">
+        <v>4.587617</v>
+      </c>
+      <c r="F18">
+        <v>3483.836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250913</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>15.125</v>
+      </c>
+      <c r="D19">
+        <v>600.5</v>
+      </c>
+      <c r="E19">
+        <v>4.487602</v>
+      </c>
+      <c r="F19">
+        <v>2694.805</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250915</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>10.533</v>
+      </c>
+      <c r="D20">
+        <v>416.8</v>
+      </c>
+      <c r="E20">
+        <v>6.365876</v>
+      </c>
+      <c r="F20">
+        <v>2653.297</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250916</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>102.001</v>
+      </c>
+      <c r="D21">
+        <v>3825.3</v>
+      </c>
+      <c r="E21">
+        <v>4.626306</v>
+      </c>
+      <c r="F21">
+        <v>17697.01</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250917</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>7.35</v>
+      </c>
+      <c r="D22">
+        <v>277.3</v>
+      </c>
+      <c r="E22">
+        <v>4.289852</v>
+      </c>
+      <c r="F22">
+        <v>1189.576</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20250918</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>21.957</v>
+      </c>
+      <c r="D23">
+        <v>781.4</v>
+      </c>
+      <c r="E23">
+        <v>5.090639</v>
+      </c>
+      <c r="F23">
+        <v>3977.825</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F23"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -2323,11 +2857,8 @@
       <c r="C4">
         <v>322</v>
       </c>
-      <c r="D4">
-        <v>178</v>
-      </c>
       <c r="E4">
-        <v>500</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +3034,10 @@
         <v>772</v>
       </c>
       <c r="D15">
-        <v>801</v>
+        <v>623</v>
       </c>
       <c r="E15">
-        <v>2159</v>
+        <v>1981</v>
       </c>
     </row>
   </sheetData>
@@ -2559,10 +3090,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>6.368</v>
+        <v>6.435</v>
       </c>
       <c r="E2">
-        <v>6.368</v>
+        <v>6.435</v>
       </c>
     </row>
     <row r="3">
@@ -2572,10 +3103,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>6.201</v>
+        <v>6.293</v>
       </c>
       <c r="E3">
-        <v>6.201</v>
+        <v>6.293</v>
       </c>
     </row>
     <row r="4">
@@ -2585,13 +3116,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>37.213</v>
+        <v>37.131</v>
       </c>
       <c r="C4">
-        <v>38.065</v>
+        <v>37.949</v>
       </c>
       <c r="E4">
-        <v>37.639</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="5">
@@ -2601,13 +3132,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.906</v>
+        <v>1.898</v>
       </c>
       <c r="C5">
-        <v>1.933</v>
+        <v>1.885</v>
       </c>
       <c r="E5">
-        <v>1.919</v>
+        <v>1.892</v>
       </c>
     </row>
     <row r="6">
@@ -2617,13 +3148,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>28.906</v>
+        <v>28.841</v>
       </c>
       <c r="C6">
-        <v>17.108</v>
+        <v>17.101</v>
       </c>
       <c r="E6">
-        <v>20.848</v>
+        <v>20.823</v>
       </c>
     </row>
   </sheetData>
@@ -37966,13 +38497,13 @@
         <v>104.045</v>
       </c>
       <c r="D2">
-        <v>655.4</v>
+        <v>650.8</v>
       </c>
       <c r="E2">
-        <v>6.200851</v>
+        <v>6.292979</v>
       </c>
       <c r="F2">
-        <v>6.299197</v>
+        <v>6.254986</v>
       </c>
     </row>
     <row r="3">
@@ -38001,13 +38532,13 @@
         <v>249.652</v>
       </c>
       <c r="D4">
-        <v>1595.9</v>
+        <v>1624.4</v>
       </c>
       <c r="E4">
-        <v>6.367909</v>
+        <v>6.434545</v>
       </c>
       <c r="F4">
-        <v>6.392498</v>
+        <v>6.506657</v>
       </c>
     </row>
     <row r="5">
@@ -38036,13 +38567,13 @@
         <v>60.62</v>
       </c>
       <c r="D6">
-        <v>115.6</v>
+        <v>112.2</v>
       </c>
       <c r="E6">
-        <v>1.905938</v>
+        <v>1.898125</v>
       </c>
       <c r="F6">
-        <v>1.906961</v>
+        <v>1.850874</v>
       </c>
     </row>
     <row r="7">
@@ -38058,13 +38589,13 @@
         <v>60.62</v>
       </c>
       <c r="D7">
-        <v>119.5</v>
+        <v>111.8</v>
       </c>
       <c r="E7">
-        <v>1.932812</v>
+        <v>1.885</v>
       </c>
       <c r="F7">
-        <v>1.971297</v>
+        <v>1.844276</v>
       </c>
     </row>
     <row r="8">
@@ -38080,13 +38611,13 @@
         <v>248.767</v>
       </c>
       <c r="D8">
-        <v>9201.5</v>
+        <v>9117.1</v>
       </c>
       <c r="E8">
-        <v>37.213462</v>
+        <v>37.130962</v>
       </c>
       <c r="F8">
-        <v>36.988427</v>
+        <v>36.649154</v>
       </c>
     </row>
     <row r="9">
@@ -38102,13 +38633,13 @@
         <v>248.767</v>
       </c>
       <c r="D9">
-        <v>9306.9</v>
+        <v>9275.8</v>
       </c>
       <c r="E9">
-        <v>38.065385</v>
+        <v>37.949423</v>
       </c>
       <c r="F9">
-        <v>37.412117</v>
+        <v>37.2871</v>
       </c>
     </row>
   </sheetData>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T19:53:32.768Z</t>
+          <t xml:space="preserve">2026-10-14T20:17:51.498Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -16,7 +16,8 @@
     <sheet name="q10 地块季 → 按作物汇总" sheetId="12" r:id="rId12"/>
     <sheet name="q11 单元 × 旬 → 按旬汇总" sheetId="13" r:id="rId13"/>
     <sheet name="q14 收获排产压力（按日）" sheetId="14" r:id="rId14"/>
-    <sheet name="q13 农事日历：月 × 事件类型（次）" sheetId="15" r:id="rId15"/>
+    <sheet name="q15 排产建议：错峰 vs 增点（三个数）" sheetId="15" r:id="rId15"/>
+    <sheet name="q13 农事日历：月 × 事件类型（次）" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -68,8 +69,454 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="zh-CN"/>
+              <a:t>收获排产压力：每日运力占用（吨·分钟）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'q14 收获排产压力（按日）'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>吨·分钟</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'q14 收获排产压力（按日）'!$A$2:$A$23</c:f>
+              <c:strCache>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>20240905</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20240920</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20250701</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20250702</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20250703</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20250704</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20250705</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20250721</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20250722</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20250723</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20250724</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20250725</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20250901</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20250908</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20250909</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20250911</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20250912</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20250913</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20250915</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20250916</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20250917</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20250918</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'q14 收获排产压力（按日）'!$F$2:$F$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>561.914</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>44795.208</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>846.637</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>886.687</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21.07</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>412.828</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1473.545</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>322.887</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>681.314</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>836.334</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>634.595</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6751.491</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>553.833</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9674.702</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3235.271</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>358.559</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3483.836</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2694.805</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2653.297</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>17697.01</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1189.576</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3977.825</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="100"/>
+        <c:axId val="200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="200"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="100"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="zh-CN"/>
+              <a:t>农事日历：各月收获次数</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'q13 农事日历：月 × 事件类型（次）'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>收获次数</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'q13 农事日历：月 × 事件类型（次）'!$A$2:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>2024-04</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024-05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2024-07</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024-09</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2024-10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2024-11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2025-04</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025-05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2025-06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2025-11</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'q13 农事日历：月 × 事件类型（次）'!$D$2:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="100"/>
+        <c:axId val="200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="200"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:crossAx val="100"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6286500" cy="3143250"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6286500" cy="3143250"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.0" customWidth="1"/>
@@ -108,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T20:17:51.498Z</t>
+          <t xml:space="preserve">2026-10-14T20:41:44.287Z</t>
         </is>
       </c>
     </row>
@@ -168,7 +615,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总; q14 收获排产压力（按日）; q13 农事日历：月 × 事件类型（次）</t>
+          <t xml:space="preserve">q1 各作物 × 各年 的平均单产; q2 各经营单元 × 各旬 的平均生长进度; q3 各网格 × 各作物 的面积; q4 观测长表 → 宽表（日期 × 变量）; q5 联合筛选：运距远 + 有机碳低 + 病级高的地块; q6 四层空间钻取链（行政区划 → 网格 → 单元 → 地块）; q7 管理分区 × 作物 的地块数与面积; q12 单产两套口径对照（季等权 vs 面积加权）; q8 区域逐日 → 按年月汇总; q9 农事事件 → 按年 × 类型计数; q10 地块季 → 按作物汇总; q11 单元 × 旬 → 按旬汇总; q14 收获排产压力（按日）; q15 排产建议：错峰 vs 增点（三个数）; q13 农事日历：月 × 事件类型（次）</t>
         </is>
       </c>
     </row>
@@ -178,7 +625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.0" customWidth="1"/>
@@ -623,7 +1070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.4" customWidth="1"/>
@@ -728,7 +1175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.4" customWidth="1"/>
@@ -847,7 +1294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.0" customWidth="1"/>
@@ -2252,7 +2699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.6" customWidth="1"/>
@@ -2781,11 +3228,103 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F23"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="22.8" customWidth="1"/>
+    <col min="2" max="2" width="8.6" customWidth="1"/>
+    <col min="3" max="3" width="7.7" customWidth="1"/>
+    <col min="4" max="4" width="48.0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>情景</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>峰值占用</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>降幅</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">现状（峰值日）</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>44795.2</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20240920：44795.2 t·min（= q14 的最大值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">错峰（摊到前后各 3 天）</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>24096.3</v>
+      </c>
+      <c r="C3">
+        <v>0.4621</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每天新增 = 峰值占用 ÷ 7；再取摊完后的新峰值（另 6 天本来就有收获）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">增点（建在受益最大处）</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>33075.6</v>
+      </c>
+      <c r="C4">
+        <v>0.2616</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">候选 11.5818,48.6078（591.6 ha 受益）只作用在**峰值日**的待收地块上</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.6" customWidth="1"/>
@@ -3042,11 +3581,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E15"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="43.6" customWidth="1"/>
@@ -3163,7 +3703,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.2" customWidth="1"/>
@@ -14348,7 +14888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.3" customWidth="1"/>
@@ -17825,7 +18365,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="26.0" customWidth="1"/>
@@ -36598,7 +37138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.4" customWidth="1"/>
@@ -38147,7 +38687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.0" customWidth="1"/>
@@ -38271,7 +38811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.4" customWidth="1"/>
@@ -38441,7 +38981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14T20:41:44.287Z</t>
+          <t xml:space="preserve">2026-10-15T20:04:55.397Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15T20:04:55.397Z</t>
+          <t xml:space="preserve">2026-10-15T20:44:16.227Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15T20:44:16.227Z</t>
+          <t xml:space="preserve">2026-10-16T06:11:25.438Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T06:11:25.438Z</t>
+          <t xml:space="preserve">2026-10-16T07:11:51.461Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T07:11:51.461Z</t>
+          <t xml:space="preserve">2026-10-16T07:55:49.883Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T07:55:49.883Z</t>
+          <t xml:space="preserve">2026-10-16T08:18:23.244Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T08:18:23.244Z</t>
+          <t xml:space="preserve">2026-10-16T08:25:45.653Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T08:25:45.653Z</t>
+          <t xml:space="preserve">2026-10-16T08:59:17.574Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T08:59:17.574Z</t>
+          <t xml:space="preserve">2026-10-16T09:39:06.415Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16T09:39:06.415Z</t>
+          <t xml:space="preserve">2026-10-17T13:13:51.092Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17T13:13:51.092Z</t>
+          <t xml:space="preserve">2026-10-17T13:44:34.539Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17T13:44:34.539Z</t>
+          <t xml:space="preserve">2026-10-17T13:49:17.061Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17T13:49:17.061Z</t>
+          <t xml:space="preserve">2026-10-17T14:17:15.769Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17T14:17:15.769Z</t>
+          <t xml:space="preserve">2026-10-17T14:55:57.246Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17T14:55:57.246Z</t>
+          <t xml:space="preserve">2026-10-17T15:15:38.843Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17T15:15:38.843Z</t>
+          <t xml:space="preserve">2026-10-18T04:51:17.495Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18T04:51:17.495Z</t>
+          <t xml:space="preserve">2026-10-18T19:54:17.574Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18T19:54:17.574Z</t>
+          <t xml:space="preserve">2026-10-18T20:01:46.177Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18T20:01:46.177Z</t>
+          <t xml:space="preserve">2026-10-18T20:08:13.409Z</t>
         </is>
       </c>
     </row>

--- a/tables/query/透视与联合查询.xlsx
+++ b/tables/query/透视与联合查询.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18T20:08:13.409Z</t>
+          <t xml:space="preserve">2026-10-18T21:16:55.751Z</t>
         </is>
       </c>
     </row>
